--- a/KAYZEN-Portfel-Maliyye-48ay-v3.xlsx
+++ b/KAYZEN-Portfel-Maliyye-48ay-v3.xlsx
@@ -68,11 +68,11 @@
       <sz val="8"/>
     </font>
     <font>
-      <b val="1"/>
+      <color rgb="00FFE4A8"/>
       <sz val="8"/>
     </font>
     <font>
-      <color rgb="00FFE4A8"/>
+      <b val="1"/>
       <sz val="8"/>
     </font>
     <font>
@@ -203,10 +203,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1700000</v>
+        <v>1620000</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>439236.3055454039</v>
+        <v>507374.2489718552</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>-1360763.694454596</v>
+        <v>-1292625.751028144</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>44800.08869291328</v>
+        <v>52617.73039626619</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>316249.2851594975</v>
+        <v>366479.3090406646</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>1013820.005432606</v>
+        <v>1190154.091906566</v>
       </c>
     </row>
     <row r="13">
@@ -775,13 +775,13 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>537601.0643149593</v>
+        <v>631412.7647551943</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>3794991.421913969</v>
+        <v>4397751.708487975</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>12165840.06519128</v>
+        <v>14281849.1028788</v>
       </c>
     </row>
     <row r="14">
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>30761.138719872</v>
+        <v>38578.78042322492</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>214588.6149402942</v>
+        <v>264818.6388214613</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>756100.7260236434</v>
+        <v>932434.8124976034</v>
       </c>
     </row>
     <row r="15">
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>-51123.95401276947</v>
+        <v>-45886.44226310269</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>122664.4663721388</v>
+        <v>156149.9339159759</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>595616.4533868688</v>
+        <v>712940.5472424908</v>
       </c>
     </row>
     <row r="19">
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>696955.6281371405</v>
+        <v>695732.3841091311</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>956654.4325832389</v>
+        <v>1242530.72854805</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>4960164.669747315</v>
+        <v>6090880.243555006</v>
       </c>
     </row>
     <row r="20">
@@ -1169,240 +1169,240 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>█</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="G3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="H3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="I3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="J3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="K3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="L3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="M3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="N3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="O3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="P3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="Q3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="R3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="S3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="T3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="U3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="V3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="W3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="X3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="Y3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="Z3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AA3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AB3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AC3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AD3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AE3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AF3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AG3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AH3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AI3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AJ3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AK3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AL3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AM3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AN3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AO3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AP3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AQ3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AR3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AS3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AT3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AU3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AV3" s="17" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="AW3" s="17" t="inlineStr">
+          <t>█</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="K3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="L3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="M3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="N3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="O3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="Q3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="R3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="S3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="T3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="U3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="V3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="W3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="X3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="Y3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="Z3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AA3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AB3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AC3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AD3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AE3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AF3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AG3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AH3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AI3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AJ3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AK3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AL3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AM3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AN3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AO3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AP3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AQ3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AR3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AS3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AT3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AU3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AV3" s="16" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="AW3" s="16" t="inlineStr">
         <is>
           <t>█</t>
         </is>
@@ -1414,17 +1414,17 @@
           <t>QUOTEFLOW</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K4" s="16" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L4" s="16" t="inlineStr">
+      <c r="L4" s="17" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -1621,17 +1621,17 @@
           <t>FORMCHECK</t>
         </is>
       </c>
-      <c r="R5" s="16" t="inlineStr">
+      <c r="R5" s="17" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S5" s="16" t="inlineStr">
+      <c r="S5" s="17" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="T5" s="16" t="inlineStr">
+      <c r="T5" s="17" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -1788,17 +1788,17 @@
           <t>CONFIGFLOW</t>
         </is>
       </c>
-      <c r="Z6" s="16" t="inlineStr">
+      <c r="Z6" s="17" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="AA6" s="16" t="inlineStr">
+      <c r="AA6" s="17" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="AB6" s="16" t="inlineStr">
+      <c r="AB6" s="17" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C3" s="29" t="n">
-        <v>0</v>
+        <v>2506</v>
       </c>
       <c r="D3" s="29" t="n">
         <v>0</v>
@@ -2993,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="G3" s="30" t="n">
-        <v>0</v>
+        <v>2506</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="11" t="n">
         <v>9</v>
@@ -3005,16 +3005,16 @@
         <v>28375</v>
       </c>
       <c r="K3" s="29" t="n">
-        <v>600</v>
+        <v>874</v>
       </c>
       <c r="L3" s="29" t="n">
         <v>1170</v>
       </c>
       <c r="M3" s="29" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="N3" s="29" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="O3" s="29" t="n">
         <v>17100</v>
@@ -3023,16 +3023,16 @@
         <v>1500</v>
       </c>
       <c r="Q3" s="29" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="R3" s="30" t="n">
-        <v>54745</v>
+        <v>60194</v>
       </c>
       <c r="S3" s="29" t="n">
-        <v>-54745</v>
+        <v>-57688</v>
       </c>
       <c r="T3" s="29" t="n">
-        <v>1745255</v>
+        <v>1742312</v>
       </c>
     </row>
     <row r="4">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="C4" s="29" t="n">
-        <v>0</v>
+        <v>3474</v>
       </c>
       <c r="D4" s="29" t="n">
         <v>0</v>
@@ -3057,10 +3057,10 @@
         <v>0</v>
       </c>
       <c r="G4" s="30" t="n">
-        <v>0</v>
+        <v>3474</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="11" t="n">
         <v>18</v>
@@ -3069,16 +3069,16 @@
         <v>49625</v>
       </c>
       <c r="K4" s="29" t="n">
-        <v>600</v>
+        <v>877</v>
       </c>
       <c r="L4" s="29" t="n">
         <v>2340</v>
       </c>
       <c r="M4" s="29" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="N4" s="29" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="O4" s="29" t="n">
         <v>14400</v>
@@ -3087,16 +3087,16 @@
         <v>1500</v>
       </c>
       <c r="Q4" s="29" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="R4" s="30" t="n">
-        <v>74465</v>
+        <v>79436</v>
       </c>
       <c r="S4" s="29" t="n">
-        <v>-74465</v>
+        <v>-75962</v>
       </c>
       <c r="T4" s="29" t="n">
-        <v>1670790</v>
+        <v>1666350</v>
       </c>
     </row>
     <row r="5">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="C5" s="29" t="n">
-        <v>2506</v>
+        <v>4515</v>
       </c>
       <c r="D5" s="29" t="n">
         <v>0</v>
@@ -3121,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="30" t="n">
-        <v>2506</v>
+        <v>4515</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>1</v>
@@ -3133,16 +3133,16 @@
         <v>49625</v>
       </c>
       <c r="K5" s="29" t="n">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="L5" s="29" t="n">
         <v>2340</v>
       </c>
       <c r="M5" s="29" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="N5" s="29" t="n">
-        <v>252</v>
+        <v>310</v>
       </c>
       <c r="O5" s="29" t="n">
         <v>0</v>
@@ -3151,16 +3151,16 @@
         <v>1500</v>
       </c>
       <c r="Q5" s="29" t="n">
-        <v>293</v>
+        <v>403</v>
       </c>
       <c r="R5" s="30" t="n">
-        <v>61514</v>
+        <v>65135</v>
       </c>
       <c r="S5" s="29" t="n">
-        <v>-59008</v>
+        <v>-60620</v>
       </c>
       <c r="T5" s="29" t="n">
-        <v>1611782</v>
+        <v>1605729</v>
       </c>
     </row>
     <row r="6">
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="C6" s="29" t="n">
-        <v>3474</v>
+        <v>5637</v>
       </c>
       <c r="D6" s="29" t="n">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>3474</v>
+        <v>5637</v>
       </c>
       <c r="H6" s="11" t="n">
         <v>1</v>
@@ -3197,16 +3197,16 @@
         <v>49625</v>
       </c>
       <c r="K6" s="29" t="n">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="L6" s="29" t="n">
         <v>2340</v>
       </c>
       <c r="M6" s="29" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="N6" s="29" t="n">
-        <v>280</v>
+        <v>345</v>
       </c>
       <c r="O6" s="29" t="n">
         <v>0</v>
@@ -3215,16 +3215,16 @@
         <v>1500</v>
       </c>
       <c r="Q6" s="29" t="n">
-        <v>346</v>
+        <v>466</v>
       </c>
       <c r="R6" s="30" t="n">
-        <v>61036</v>
+        <v>65244</v>
       </c>
       <c r="S6" s="29" t="n">
-        <v>-57562</v>
+        <v>-59607</v>
       </c>
       <c r="T6" s="29" t="n">
-        <v>1554220</v>
+        <v>1546123</v>
       </c>
     </row>
     <row r="7">
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="C7" s="29" t="n">
-        <v>4515</v>
+        <v>6852</v>
       </c>
       <c r="D7" s="29" t="n">
         <v>0</v>
@@ -3249,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="30" t="n">
-        <v>4515</v>
+        <v>6852</v>
       </c>
       <c r="H7" s="11" t="n">
         <v>1</v>
@@ -3261,16 +3261,16 @@
         <v>49625</v>
       </c>
       <c r="K7" s="29" t="n">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="L7" s="29" t="n">
         <v>2340</v>
       </c>
       <c r="M7" s="29" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="N7" s="29" t="n">
-        <v>310</v>
+        <v>383</v>
       </c>
       <c r="O7" s="29" t="n">
         <v>0</v>
@@ -3279,16 +3279,16 @@
         <v>1500</v>
       </c>
       <c r="Q7" s="29" t="n">
-        <v>403</v>
+        <v>535</v>
       </c>
       <c r="R7" s="30" t="n">
-        <v>61135</v>
+        <v>65364</v>
       </c>
       <c r="S7" s="29" t="n">
-        <v>-56620</v>
+        <v>-58512</v>
       </c>
       <c r="T7" s="29" t="n">
-        <v>1497599</v>
+        <v>1487611</v>
       </c>
     </row>
     <row r="8">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="C8" s="29" t="n">
-        <v>5637</v>
+        <v>8171</v>
       </c>
       <c r="D8" s="29" t="n">
         <v>0</v>
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="30" t="n">
-        <v>5637</v>
+        <v>8171</v>
       </c>
       <c r="H8" s="11" t="n">
         <v>1</v>
@@ -3325,16 +3325,16 @@
         <v>56875</v>
       </c>
       <c r="K8" s="29" t="n">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="L8" s="29" t="n">
         <v>2730</v>
       </c>
       <c r="M8" s="29" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="N8" s="29" t="n">
-        <v>345</v>
+        <v>425</v>
       </c>
       <c r="O8" s="29" t="n">
         <v>5700</v>
@@ -3343,16 +3343,16 @@
         <v>1500</v>
       </c>
       <c r="Q8" s="29" t="n">
-        <v>466</v>
+        <v>611</v>
       </c>
       <c r="R8" s="30" t="n">
-        <v>74584</v>
+        <v>78837</v>
       </c>
       <c r="S8" s="29" t="n">
-        <v>-68947</v>
+        <v>-70665</v>
       </c>
       <c r="T8" s="29" t="n">
-        <v>1428653</v>
+        <v>1416945</v>
       </c>
     </row>
     <row r="9">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="C9" s="29" t="n">
-        <v>6852</v>
+        <v>9607</v>
       </c>
       <c r="D9" s="29" t="n">
         <v>0</v>
@@ -3377,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="30" t="n">
-        <v>6852</v>
+        <v>9607</v>
       </c>
       <c r="H9" s="11" t="n">
         <v>1</v>
@@ -3389,16 +3389,16 @@
         <v>56875</v>
       </c>
       <c r="K9" s="29" t="n">
-        <v>886</v>
+        <v>895</v>
       </c>
       <c r="L9" s="29" t="n">
         <v>2730</v>
       </c>
       <c r="M9" s="29" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="N9" s="29" t="n">
-        <v>383</v>
+        <v>471</v>
       </c>
       <c r="O9" s="29" t="n">
         <v>0</v>
@@ -3407,16 +3407,16 @@
         <v>1500</v>
       </c>
       <c r="Q9" s="29" t="n">
-        <v>535</v>
+        <v>695</v>
       </c>
       <c r="R9" s="30" t="n">
-        <v>69004</v>
+        <v>73283</v>
       </c>
       <c r="S9" s="29" t="n">
-        <v>-62152</v>
+        <v>-63675</v>
       </c>
       <c r="T9" s="29" t="n">
-        <v>1366501</v>
+        <v>1353270</v>
       </c>
     </row>
     <row r="10">
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="C10" s="29" t="n">
-        <v>8171</v>
+        <v>11175</v>
       </c>
       <c r="D10" s="29" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>8171</v>
+        <v>11175</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>1</v>
@@ -3453,16 +3453,16 @@
         <v>59625</v>
       </c>
       <c r="K10" s="29" t="n">
-        <v>890</v>
+        <v>900</v>
       </c>
       <c r="L10" s="29" t="n">
         <v>2860</v>
       </c>
       <c r="M10" s="29" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="N10" s="29" t="n">
-        <v>425</v>
+        <v>523</v>
       </c>
       <c r="O10" s="29" t="n">
         <v>2200</v>
@@ -3471,16 +3471,16 @@
         <v>1500</v>
       </c>
       <c r="Q10" s="29" t="n">
-        <v>611</v>
+        <v>787</v>
       </c>
       <c r="R10" s="30" t="n">
-        <v>74217</v>
+        <v>78525</v>
       </c>
       <c r="S10" s="29" t="n">
-        <v>-66045</v>
+        <v>-67349</v>
       </c>
       <c r="T10" s="29" t="n">
-        <v>1300455</v>
+        <v>1285921</v>
       </c>
     </row>
     <row r="11">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="C11" s="29" t="n">
-        <v>9607</v>
+        <v>12891</v>
       </c>
       <c r="D11" s="29" t="n">
         <v>980</v>
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="30" t="n">
-        <v>10587</v>
+        <v>13871</v>
       </c>
       <c r="H11" s="11" t="n">
         <v>2</v>
@@ -3517,16 +3517,16 @@
         <v>65000</v>
       </c>
       <c r="K11" s="29" t="n">
-        <v>1145</v>
+        <v>1155</v>
       </c>
       <c r="L11" s="29" t="n">
         <v>3120</v>
       </c>
       <c r="M11" s="29" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="N11" s="29" t="n">
-        <v>471</v>
+        <v>581</v>
       </c>
       <c r="O11" s="29" t="n">
         <v>2600</v>
@@ -3535,16 +3535,16 @@
         <v>1500</v>
       </c>
       <c r="Q11" s="29" t="n">
-        <v>723</v>
+        <v>917</v>
       </c>
       <c r="R11" s="30" t="n">
-        <v>80676</v>
+        <v>85017</v>
       </c>
       <c r="S11" s="29" t="n">
-        <v>-70089</v>
+        <v>-71146</v>
       </c>
       <c r="T11" s="29" t="n">
-        <v>1230366</v>
+        <v>1214774</v>
       </c>
     </row>
     <row r="12">
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="C12" s="29" t="n">
-        <v>11175</v>
+        <v>14771</v>
       </c>
       <c r="D12" s="29" t="n">
         <v>1994</v>
@@ -3569,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="30" t="n">
-        <v>13170</v>
+        <v>16765</v>
       </c>
       <c r="H12" s="11" t="n">
         <v>2</v>
@@ -3581,16 +3581,16 @@
         <v>65000</v>
       </c>
       <c r="K12" s="29" t="n">
-        <v>1150</v>
+        <v>1161</v>
       </c>
       <c r="L12" s="29" t="n">
         <v>3120</v>
       </c>
       <c r="M12" s="29" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="N12" s="29" t="n">
-        <v>523</v>
+        <v>645</v>
       </c>
       <c r="O12" s="29" t="n">
         <v>0</v>
@@ -3599,16 +3599,16 @@
         <v>1500</v>
       </c>
       <c r="Q12" s="29" t="n">
-        <v>845</v>
+        <v>1059</v>
       </c>
       <c r="R12" s="30" t="n">
-        <v>78267</v>
+        <v>82645</v>
       </c>
       <c r="S12" s="29" t="n">
-        <v>-65098</v>
+        <v>-65879</v>
       </c>
       <c r="T12" s="29" t="n">
-        <v>1165269</v>
+        <v>1148895</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="C13" s="29" t="n">
-        <v>12891</v>
+        <v>16835</v>
       </c>
       <c r="D13" s="29" t="n">
         <v>3047</v>
@@ -3633,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="30" t="n">
-        <v>15938</v>
+        <v>19882</v>
       </c>
       <c r="H13" s="11" t="n">
         <v>2</v>
@@ -3645,16 +3645,16 @@
         <v>65000</v>
       </c>
       <c r="K13" s="29" t="n">
-        <v>1155</v>
+        <v>1168</v>
       </c>
       <c r="L13" s="29" t="n">
         <v>3120</v>
       </c>
       <c r="M13" s="29" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="N13" s="29" t="n">
-        <v>581</v>
+        <v>716</v>
       </c>
       <c r="O13" s="29" t="n">
         <v>0</v>
@@ -3663,16 +3663,16 @@
         <v>1500</v>
       </c>
       <c r="Q13" s="29" t="n">
-        <v>977</v>
+        <v>1213</v>
       </c>
       <c r="R13" s="30" t="n">
-        <v>78477</v>
+        <v>82894</v>
       </c>
       <c r="S13" s="29" t="n">
-        <v>-62539</v>
+        <v>-63012</v>
       </c>
       <c r="T13" s="29" t="n">
-        <v>1102729</v>
+        <v>1085883</v>
       </c>
     </row>
     <row r="14">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="C14" s="29" t="n">
-        <v>14771</v>
+        <v>19106</v>
       </c>
       <c r="D14" s="29" t="n">
         <v>4143</v>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="30" t="n">
-        <v>18913</v>
+        <v>23248</v>
       </c>
       <c r="H14" s="11" t="n">
         <v>2</v>
@@ -3709,16 +3709,16 @@
         <v>66625</v>
       </c>
       <c r="K14" s="29" t="n">
-        <v>1161</v>
+        <v>1176</v>
       </c>
       <c r="L14" s="29" t="n">
         <v>3250</v>
       </c>
       <c r="M14" s="29" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="N14" s="29" t="n">
-        <v>645</v>
+        <v>794</v>
       </c>
       <c r="O14" s="29" t="n">
         <v>1300</v>
@@ -3727,16 +3727,16 @@
         <v>1500</v>
       </c>
       <c r="Q14" s="29" t="n">
-        <v>1121</v>
+        <v>1383</v>
       </c>
       <c r="R14" s="30" t="n">
-        <v>81762</v>
+        <v>86224</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>-62848</v>
+        <v>-62976</v>
       </c>
       <c r="T14" s="29" t="n">
-        <v>1039881</v>
+        <v>1022907</v>
       </c>
     </row>
     <row r="15">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="C15" s="29" t="n">
-        <v>16835</v>
+        <v>21606</v>
       </c>
       <c r="D15" s="29" t="n">
         <v>5286</v>
@@ -3761,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="30" t="n">
-        <v>22121</v>
+        <v>26891</v>
       </c>
       <c r="H15" s="11" t="n">
         <v>2</v>
@@ -3773,16 +3773,16 @@
         <v>70125</v>
       </c>
       <c r="K15" s="29" t="n">
-        <v>1168</v>
+        <v>1184</v>
       </c>
       <c r="L15" s="29" t="n">
         <v>3380</v>
       </c>
       <c r="M15" s="29" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="N15" s="29" t="n">
-        <v>716</v>
+        <v>882</v>
       </c>
       <c r="O15" s="29" t="n">
         <v>2200</v>
@@ -3791,16 +3791,16 @@
         <v>1900</v>
       </c>
       <c r="Q15" s="29" t="n">
-        <v>1278</v>
+        <v>1568</v>
       </c>
       <c r="R15" s="30" t="n">
-        <v>86944</v>
+        <v>91457</v>
       </c>
       <c r="S15" s="29" t="n">
-        <v>-64823</v>
+        <v>-64566</v>
       </c>
       <c r="T15" s="29" t="n">
-        <v>975058</v>
+        <v>958341</v>
       </c>
     </row>
     <row r="16">
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="C16" s="29" t="n">
-        <v>19106</v>
+        <v>24361</v>
       </c>
       <c r="D16" s="29" t="n">
         <v>6481</v>
@@ -3825,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="30" t="n">
-        <v>25587</v>
+        <v>30843</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>2</v>
@@ -3837,16 +3837,16 @@
         <v>70125</v>
       </c>
       <c r="K16" s="29" t="n">
-        <v>1176</v>
+        <v>1193</v>
       </c>
       <c r="L16" s="29" t="n">
         <v>3380</v>
       </c>
       <c r="M16" s="29" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="N16" s="29" t="n">
-        <v>794</v>
+        <v>979</v>
       </c>
       <c r="O16" s="29" t="n">
         <v>0</v>
@@ -3855,16 +3855,16 @@
         <v>1900</v>
       </c>
       <c r="Q16" s="29" t="n">
-        <v>1450</v>
+        <v>1771</v>
       </c>
       <c r="R16" s="30" t="n">
-        <v>85022</v>
+        <v>89590</v>
       </c>
       <c r="S16" s="29" t="n">
-        <v>-59435</v>
+        <v>-58748</v>
       </c>
       <c r="T16" s="29" t="n">
-        <v>915622</v>
+        <v>899594</v>
       </c>
     </row>
     <row r="17">
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="C17" s="29" t="n">
-        <v>21606</v>
+        <v>27403</v>
       </c>
       <c r="D17" s="29" t="n">
         <v>7734</v>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="30" t="n">
-        <v>29340</v>
+        <v>35137</v>
       </c>
       <c r="H17" s="11" t="n">
         <v>2</v>
@@ -3901,16 +3901,16 @@
         <v>72250</v>
       </c>
       <c r="K17" s="29" t="n">
-        <v>1184</v>
+        <v>1203</v>
       </c>
       <c r="L17" s="29" t="n">
         <v>3510</v>
       </c>
       <c r="M17" s="29" t="n">
-        <v>6455</v>
+        <v>10000</v>
       </c>
       <c r="N17" s="29" t="n">
-        <v>882</v>
+        <v>1086</v>
       </c>
       <c r="O17" s="29" t="n">
         <v>1300</v>
@@ -3919,16 +3919,16 @@
         <v>1900</v>
       </c>
       <c r="Q17" s="29" t="n">
-        <v>1639</v>
+        <v>1994</v>
       </c>
       <c r="R17" s="30" t="n">
-        <v>89338</v>
+        <v>93513</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>-59998</v>
+        <v>-58376</v>
       </c>
       <c r="T17" s="29" t="n">
-        <v>855625</v>
+        <v>841218</v>
       </c>
     </row>
     <row r="18">
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="C18" s="29" t="n">
-        <v>24361</v>
+        <v>30761</v>
       </c>
       <c r="D18" s="29" t="n">
         <v>9051</v>
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="30" t="n">
-        <v>34114</v>
+        <v>40514</v>
       </c>
       <c r="H18" s="11" t="n">
         <v>3</v>
@@ -3965,16 +3965,16 @@
         <v>72250</v>
       </c>
       <c r="K18" s="29" t="n">
-        <v>1443</v>
+        <v>1465</v>
       </c>
       <c r="L18" s="29" t="n">
         <v>3510</v>
       </c>
       <c r="M18" s="29" t="n">
-        <v>7505</v>
+        <v>10000</v>
       </c>
       <c r="N18" s="29" t="n">
-        <v>979</v>
+        <v>1206</v>
       </c>
       <c r="O18" s="29" t="n">
         <v>0</v>
@@ -3983,16 +3983,16 @@
         <v>1900</v>
       </c>
       <c r="Q18" s="29" t="n">
-        <v>1866</v>
+        <v>2259</v>
       </c>
       <c r="R18" s="30" t="n">
-        <v>89695</v>
+        <v>92889</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>-55581</v>
+        <v>-52375</v>
       </c>
       <c r="T18" s="29" t="n">
-        <v>800044</v>
+        <v>788843</v>
       </c>
     </row>
     <row r="19">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="C19" s="29" t="n">
-        <v>27403</v>
+        <v>34473</v>
       </c>
       <c r="D19" s="29" t="n">
         <v>10437</v>
@@ -4017,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="30" t="n">
-        <v>39254</v>
+        <v>46324</v>
       </c>
       <c r="H19" s="11" t="n">
         <v>3</v>
@@ -4029,16 +4029,16 @@
         <v>72250</v>
       </c>
       <c r="K19" s="29" t="n">
-        <v>1453</v>
+        <v>1477</v>
       </c>
       <c r="L19" s="29" t="n">
         <v>3510</v>
       </c>
       <c r="M19" s="29" t="n">
-        <v>8636</v>
+        <v>10191</v>
       </c>
       <c r="N19" s="29" t="n">
-        <v>1086</v>
+        <v>1338</v>
       </c>
       <c r="O19" s="29" t="n">
         <v>0</v>
@@ -4047,16 +4047,16 @@
         <v>1900</v>
       </c>
       <c r="Q19" s="29" t="n">
-        <v>2113</v>
+        <v>2550</v>
       </c>
       <c r="R19" s="30" t="n">
-        <v>91218</v>
+        <v>93549</v>
       </c>
       <c r="S19" s="29" t="n">
-        <v>-51964</v>
+        <v>-47224</v>
       </c>
       <c r="T19" s="29" t="n">
-        <v>748080</v>
+        <v>741619</v>
       </c>
     </row>
     <row r="20">
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="C20" s="32" t="n">
-        <v>30761</v>
+        <v>38579</v>
       </c>
       <c r="D20" s="32" t="n">
         <v>11898</v>
@@ -4081,7 +4081,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="33" t="n">
-        <v>44800</v>
+        <v>52618</v>
       </c>
       <c r="H20" s="34" t="n">
         <v>3</v>
@@ -4093,16 +4093,16 @@
         <v>73875</v>
       </c>
       <c r="K20" s="32" t="n">
-        <v>1465</v>
+        <v>1491</v>
       </c>
       <c r="L20" s="32" t="n">
         <v>3640</v>
       </c>
       <c r="M20" s="32" t="n">
-        <v>9856</v>
+        <v>11576</v>
       </c>
       <c r="N20" s="32" t="n">
-        <v>1206</v>
+        <v>1486</v>
       </c>
       <c r="O20" s="32" t="n">
         <v>1300</v>
@@ -4111,16 +4111,16 @@
         <v>1900</v>
       </c>
       <c r="Q20" s="32" t="n">
-        <v>2384</v>
+        <v>2868</v>
       </c>
       <c r="R20" s="33" t="n">
-        <v>95924</v>
+        <v>98504</v>
       </c>
       <c r="S20" s="32" t="n">
-        <v>-51124</v>
+        <v>-45886</v>
       </c>
       <c r="T20" s="32" t="n">
-        <v>696956</v>
+        <v>695732</v>
       </c>
     </row>
     <row r="21">
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="C21" s="29" t="n">
-        <v>34473</v>
+        <v>43122</v>
       </c>
       <c r="D21" s="29" t="n">
         <v>13442</v>
@@ -4145,7 +4145,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>50800</v>
+        <v>59448</v>
       </c>
       <c r="H21" s="11" t="n">
         <v>3</v>
@@ -4157,16 +4157,16 @@
         <v>73875</v>
       </c>
       <c r="K21" s="29" t="n">
-        <v>1477</v>
+        <v>1507</v>
       </c>
       <c r="L21" s="29" t="n">
         <v>3640</v>
       </c>
       <c r="M21" s="29" t="n">
-        <v>11176</v>
+        <v>13079</v>
       </c>
       <c r="N21" s="29" t="n">
-        <v>1338</v>
+        <v>1649</v>
       </c>
       <c r="O21" s="29" t="n">
         <v>0</v>
@@ -4175,16 +4175,16 @@
         <v>1900</v>
       </c>
       <c r="Q21" s="29" t="n">
-        <v>2680</v>
+        <v>3217</v>
       </c>
       <c r="R21" s="30" t="n">
-        <v>96418</v>
+        <v>99276</v>
       </c>
       <c r="S21" s="29" t="n">
-        <v>-45618</v>
+        <v>-39827</v>
       </c>
       <c r="T21" s="29" t="n">
-        <v>651337</v>
+        <v>655905</v>
       </c>
     </row>
     <row r="22">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="C22" s="29" t="n">
-        <v>38579</v>
+        <v>48152</v>
       </c>
       <c r="D22" s="29" t="n">
         <v>15076</v>
@@ -4209,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="30" t="n">
-        <v>57303</v>
+        <v>66876</v>
       </c>
       <c r="H22" s="11" t="n">
         <v>3</v>
@@ -4221,16 +4221,16 @@
         <v>73875</v>
       </c>
       <c r="K22" s="29" t="n">
-        <v>1491</v>
+        <v>1524</v>
       </c>
       <c r="L22" s="29" t="n">
         <v>3640</v>
       </c>
       <c r="M22" s="29" t="n">
-        <v>12607</v>
+        <v>14713</v>
       </c>
       <c r="N22" s="29" t="n">
-        <v>1486</v>
+        <v>1830</v>
       </c>
       <c r="O22" s="29" t="n">
         <v>0</v>
@@ -4239,16 +4239,16 @@
         <v>1900</v>
       </c>
       <c r="Q22" s="29" t="n">
-        <v>3004</v>
+        <v>3601</v>
       </c>
       <c r="R22" s="30" t="n">
-        <v>98371</v>
+        <v>101537</v>
       </c>
       <c r="S22" s="29" t="n">
-        <v>-41068</v>
+        <v>-34661</v>
       </c>
       <c r="T22" s="29" t="n">
-        <v>610270</v>
+        <v>621244</v>
       </c>
     </row>
     <row r="23">
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="C23" s="29" t="n">
-        <v>43122</v>
+        <v>53722</v>
       </c>
       <c r="D23" s="29" t="n">
         <v>16807</v>
@@ -4273,7 +4273,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="30" t="n">
-        <v>64366</v>
+        <v>74967</v>
       </c>
       <c r="H23" s="11" t="n">
         <v>3</v>
@@ -4285,16 +4285,16 @@
         <v>77375</v>
       </c>
       <c r="K23" s="29" t="n">
-        <v>1507</v>
+        <v>1543</v>
       </c>
       <c r="L23" s="29" t="n">
         <v>3770</v>
       </c>
       <c r="M23" s="29" t="n">
-        <v>14161</v>
+        <v>16493</v>
       </c>
       <c r="N23" s="29" t="n">
-        <v>1649</v>
+        <v>2032</v>
       </c>
       <c r="O23" s="29" t="n">
         <v>2200</v>
@@ -4303,16 +4303,16 @@
         <v>1900</v>
       </c>
       <c r="Q23" s="29" t="n">
-        <v>3360</v>
+        <v>4023</v>
       </c>
       <c r="R23" s="30" t="n">
-        <v>106330</v>
+        <v>109839</v>
       </c>
       <c r="S23" s="29" t="n">
-        <v>-41964</v>
+        <v>-34872</v>
       </c>
       <c r="T23" s="29" t="n">
-        <v>568306</v>
+        <v>586372</v>
       </c>
     </row>
     <row r="24">
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="C24" s="29" t="n">
-        <v>48152</v>
+        <v>59894</v>
       </c>
       <c r="D24" s="29" t="n">
         <v>18644</v>
@@ -4337,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="30" t="n">
-        <v>72050</v>
+        <v>83793</v>
       </c>
       <c r="H24" s="11" t="n">
         <v>3</v>
@@ -4349,16 +4349,16 @@
         <v>77375</v>
       </c>
       <c r="K24" s="29" t="n">
-        <v>1524</v>
+        <v>1565</v>
       </c>
       <c r="L24" s="29" t="n">
         <v>3770</v>
       </c>
       <c r="M24" s="29" t="n">
-        <v>15851</v>
+        <v>18434</v>
       </c>
       <c r="N24" s="29" t="n">
-        <v>1830</v>
+        <v>2255</v>
       </c>
       <c r="O24" s="29" t="n">
         <v>0</v>
@@ -4367,16 +4367,16 @@
         <v>1900</v>
       </c>
       <c r="Q24" s="29" t="n">
-        <v>3751</v>
+        <v>4487</v>
       </c>
       <c r="R24" s="30" t="n">
-        <v>106455</v>
+        <v>110345</v>
       </c>
       <c r="S24" s="29" t="n">
-        <v>-34405</v>
+        <v>-26552</v>
       </c>
       <c r="T24" s="29" t="n">
-        <v>533901</v>
+        <v>559820</v>
       </c>
     </row>
     <row r="25">
@@ -4389,7 +4389,7 @@
         </is>
       </c>
       <c r="C25" s="29" t="n">
-        <v>53722</v>
+        <v>66735</v>
       </c>
       <c r="D25" s="29" t="n">
         <v>20595</v>
@@ -4401,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="30" t="n">
-        <v>80422</v>
+        <v>93434</v>
       </c>
       <c r="H25" s="11" t="n">
         <v>3</v>
@@ -4413,16 +4413,16 @@
         <v>80125</v>
       </c>
       <c r="K25" s="29" t="n">
-        <v>1543</v>
+        <v>1588</v>
       </c>
       <c r="L25" s="29" t="n">
         <v>3900</v>
       </c>
       <c r="M25" s="29" t="n">
-        <v>17693</v>
+        <v>20556</v>
       </c>
       <c r="N25" s="29" t="n">
-        <v>2032</v>
+        <v>2503</v>
       </c>
       <c r="O25" s="29" t="n">
         <v>2200</v>
@@ -4431,16 +4431,16 @@
         <v>1900</v>
       </c>
       <c r="Q25" s="29" t="n">
-        <v>4181</v>
+        <v>4998</v>
       </c>
       <c r="R25" s="30" t="n">
-        <v>114077</v>
+        <v>118391</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>-33655</v>
+        <v>-24956</v>
       </c>
       <c r="T25" s="29" t="n">
-        <v>500246</v>
+        <v>534864</v>
       </c>
     </row>
     <row r="26">
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="C26" s="29" t="n">
-        <v>59894</v>
+        <v>74318</v>
       </c>
       <c r="D26" s="29" t="n">
         <v>22671</v>
@@ -4465,7 +4465,7 @@
         <v>1068</v>
       </c>
       <c r="G26" s="30" t="n">
-        <v>90624</v>
+        <v>105048</v>
       </c>
       <c r="H26" s="11" t="n">
         <v>4</v>
@@ -4477,16 +4477,16 @@
         <v>82375</v>
       </c>
       <c r="K26" s="29" t="n">
-        <v>1815</v>
+        <v>1865</v>
       </c>
       <c r="L26" s="29" t="n">
         <v>4030</v>
       </c>
       <c r="M26" s="29" t="n">
-        <v>19937</v>
+        <v>23110</v>
       </c>
       <c r="N26" s="29" t="n">
-        <v>2255</v>
+        <v>2779</v>
       </c>
       <c r="O26" s="29" t="n">
         <v>1300</v>
@@ -4495,16 +4495,16 @@
         <v>1900</v>
       </c>
       <c r="Q26" s="29" t="n">
-        <v>4685</v>
+        <v>5593</v>
       </c>
       <c r="R26" s="30" t="n">
-        <v>118856</v>
+        <v>123640</v>
       </c>
       <c r="S26" s="29" t="n">
-        <v>-28232</v>
+        <v>-18593</v>
       </c>
       <c r="T26" s="29" t="n">
-        <v>472013</v>
+        <v>516272</v>
       </c>
     </row>
     <row r="27">
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="C27" s="29" t="n">
-        <v>66735</v>
+        <v>82727</v>
       </c>
       <c r="D27" s="29" t="n">
         <v>24881</v>
@@ -4529,7 +4529,7 @@
         <v>2163</v>
       </c>
       <c r="G27" s="30" t="n">
-        <v>101696</v>
+        <v>117688</v>
       </c>
       <c r="H27" s="11" t="n">
         <v>4</v>
@@ -4541,16 +4541,16 @@
         <v>82375</v>
       </c>
       <c r="K27" s="29" t="n">
-        <v>1838</v>
+        <v>1894</v>
       </c>
       <c r="L27" s="29" t="n">
         <v>4030</v>
       </c>
       <c r="M27" s="29" t="n">
-        <v>22373</v>
+        <v>25891</v>
       </c>
       <c r="N27" s="29" t="n">
-        <v>2503</v>
+        <v>3084</v>
       </c>
       <c r="O27" s="29" t="n">
         <v>0</v>
@@ -4559,16 +4559,16 @@
         <v>2300</v>
       </c>
       <c r="Q27" s="29" t="n">
-        <v>5238</v>
+        <v>6247</v>
       </c>
       <c r="R27" s="30" t="n">
-        <v>121278</v>
+        <v>126585</v>
       </c>
       <c r="S27" s="29" t="n">
-        <v>-19582</v>
+        <v>-8897</v>
       </c>
       <c r="T27" s="29" t="n">
-        <v>452431</v>
+        <v>507374</v>
       </c>
     </row>
     <row r="28">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="C28" s="29" t="n">
-        <v>74318</v>
+        <v>92053</v>
       </c>
       <c r="D28" s="29" t="n">
         <v>27237</v>
@@ -4593,7 +4593,7 @@
         <v>3289</v>
       </c>
       <c r="G28" s="30" t="n">
-        <v>113733</v>
+        <v>131468</v>
       </c>
       <c r="H28" s="11" t="n">
         <v>4</v>
@@ -4605,16 +4605,16 @@
         <v>82375</v>
       </c>
       <c r="K28" s="29" t="n">
-        <v>1865</v>
+        <v>1926</v>
       </c>
       <c r="L28" s="29" t="n">
         <v>4030</v>
       </c>
       <c r="M28" s="29" t="n">
-        <v>25021</v>
+        <v>28923</v>
       </c>
       <c r="N28" s="29" t="n">
-        <v>2779</v>
+        <v>3424</v>
       </c>
       <c r="O28" s="29" t="n">
         <v>0</v>
@@ -4623,16 +4623,16 @@
         <v>2300</v>
       </c>
       <c r="Q28" s="29" t="n">
-        <v>5845</v>
+        <v>6966</v>
       </c>
       <c r="R28" s="30" t="n">
-        <v>124903</v>
+        <v>130792</v>
       </c>
       <c r="S28" s="29" t="n">
-        <v>-11170</v>
+        <v>676</v>
       </c>
       <c r="T28" s="29" t="n">
-        <v>441261</v>
+        <v>508050</v>
       </c>
     </row>
     <row r="29">
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="C29" s="29" t="n">
-        <v>82727</v>
+        <v>102398</v>
       </c>
       <c r="D29" s="29" t="n">
         <v>29750</v>
@@ -4657,7 +4657,7 @@
         <v>4451</v>
       </c>
       <c r="G29" s="30" t="n">
-        <v>126839</v>
+        <v>146510</v>
       </c>
       <c r="H29" s="11" t="n">
         <v>4</v>
@@ -4669,16 +4669,16 @@
         <v>82375</v>
       </c>
       <c r="K29" s="29" t="n">
-        <v>1894</v>
+        <v>1962</v>
       </c>
       <c r="L29" s="29" t="n">
         <v>4030</v>
       </c>
       <c r="M29" s="29" t="n">
-        <v>27905</v>
+        <v>32232</v>
       </c>
       <c r="N29" s="29" t="n">
-        <v>3084</v>
+        <v>3800</v>
       </c>
       <c r="O29" s="29" t="n">
         <v>0</v>
@@ -4687,16 +4687,16 @@
         <v>2300</v>
       </c>
       <c r="Q29" s="29" t="n">
-        <v>6512</v>
+        <v>7758</v>
       </c>
       <c r="R29" s="30" t="n">
-        <v>128864</v>
+        <v>135399</v>
       </c>
       <c r="S29" s="29" t="n">
-        <v>-2025</v>
+        <v>11111</v>
       </c>
       <c r="T29" s="29" t="n">
-        <v>439236</v>
+        <v>519161</v>
       </c>
     </row>
     <row r="30">
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C30" s="29" t="n">
-        <v>92053</v>
+        <v>113875</v>
       </c>
       <c r="D30" s="29" t="n">
         <v>32432</v>
@@ -4721,7 +4721,7 @@
         <v>5655</v>
       </c>
       <c r="G30" s="30" t="n">
-        <v>141128</v>
+        <v>162950</v>
       </c>
       <c r="H30" s="11" t="n">
         <v>4</v>
@@ -4733,16 +4733,16 @@
         <v>85500</v>
       </c>
       <c r="K30" s="29" t="n">
-        <v>1926</v>
+        <v>2002</v>
       </c>
       <c r="L30" s="29" t="n">
         <v>4160</v>
       </c>
       <c r="M30" s="29" t="n">
-        <v>31048</v>
+        <v>35849</v>
       </c>
       <c r="N30" s="29" t="n">
-        <v>3424</v>
+        <v>4218</v>
       </c>
       <c r="O30" s="29" t="n">
         <v>1300</v>
@@ -4751,16 +4751,16 @@
         <v>2300</v>
       </c>
       <c r="Q30" s="29" t="n">
-        <v>7246</v>
+        <v>8631</v>
       </c>
       <c r="R30" s="30" t="n">
-        <v>137752</v>
+        <v>145005</v>
       </c>
       <c r="S30" s="29" t="n">
-        <v>3376</v>
+        <v>17945</v>
       </c>
       <c r="T30" s="29" t="n">
-        <v>442612</v>
+        <v>537105</v>
       </c>
     </row>
     <row r="31">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="C31" s="29" t="n">
-        <v>102398</v>
+        <v>126609</v>
       </c>
       <c r="D31" s="29" t="n">
         <v>35298</v>
@@ -4785,7 +4785,7 @@
         <v>6905</v>
       </c>
       <c r="G31" s="30" t="n">
-        <v>156727</v>
+        <v>180938</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>4</v>
@@ -4797,16 +4797,16 @@
         <v>85500</v>
       </c>
       <c r="K31" s="29" t="n">
-        <v>1962</v>
+        <v>2046</v>
       </c>
       <c r="L31" s="29" t="n">
         <v>4160</v>
       </c>
       <c r="M31" s="29" t="n">
-        <v>34480</v>
+        <v>39806</v>
       </c>
       <c r="N31" s="29" t="n">
-        <v>3800</v>
+        <v>4682</v>
       </c>
       <c r="O31" s="29" t="n">
         <v>0</v>
@@ -4815,16 +4815,16 @@
         <v>2300</v>
       </c>
       <c r="Q31" s="29" t="n">
-        <v>8055</v>
+        <v>9594</v>
       </c>
       <c r="R31" s="30" t="n">
-        <v>141198</v>
+        <v>149249</v>
       </c>
       <c r="S31" s="29" t="n">
-        <v>15529</v>
+        <v>31689</v>
       </c>
       <c r="T31" s="29" t="n">
-        <v>458141</v>
+        <v>568795</v>
       </c>
     </row>
     <row r="32">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="C32" s="29" t="n">
-        <v>113875</v>
+        <v>140740</v>
       </c>
       <c r="D32" s="29" t="n">
         <v>38361</v>
@@ -4849,7 +4849,7 @@
         <v>8208</v>
       </c>
       <c r="G32" s="30" t="n">
-        <v>173775</v>
+        <v>200640</v>
       </c>
       <c r="H32" s="11" t="n">
         <v>4</v>
@@ -4861,16 +4861,16 @@
         <v>85500</v>
       </c>
       <c r="K32" s="29" t="n">
-        <v>2002</v>
+        <v>2095</v>
       </c>
       <c r="L32" s="29" t="n">
         <v>4160</v>
       </c>
       <c r="M32" s="29" t="n">
-        <v>38230</v>
+        <v>44141</v>
       </c>
       <c r="N32" s="29" t="n">
-        <v>4218</v>
+        <v>5197</v>
       </c>
       <c r="O32" s="29" t="n">
         <v>0</v>
@@ -4879,16 +4879,16 @@
         <v>2300</v>
       </c>
       <c r="Q32" s="29" t="n">
-        <v>8945</v>
+        <v>10657</v>
       </c>
       <c r="R32" s="30" t="n">
-        <v>146401</v>
+        <v>155337</v>
       </c>
       <c r="S32" s="29" t="n">
-        <v>27374</v>
+        <v>45302</v>
       </c>
       <c r="T32" s="29" t="n">
-        <v>485516</v>
+        <v>614097</v>
       </c>
     </row>
     <row r="33">
@@ -4901,7 +4901,7 @@
         </is>
       </c>
       <c r="C33" s="29" t="n">
-        <v>126609</v>
+        <v>156421</v>
       </c>
       <c r="D33" s="29" t="n">
         <v>41638</v>
@@ -4913,7 +4913,7 @@
         <v>9570</v>
       </c>
       <c r="G33" s="30" t="n">
-        <v>192424</v>
+        <v>222237</v>
       </c>
       <c r="H33" s="11" t="n">
         <v>4</v>
@@ -4925,16 +4925,16 @@
         <v>85500</v>
       </c>
       <c r="K33" s="29" t="n">
-        <v>2046</v>
+        <v>2149</v>
       </c>
       <c r="L33" s="29" t="n">
         <v>4160</v>
       </c>
       <c r="M33" s="29" t="n">
-        <v>42333</v>
+        <v>48892</v>
       </c>
       <c r="N33" s="29" t="n">
-        <v>4682</v>
+        <v>5769</v>
       </c>
       <c r="O33" s="29" t="n">
         <v>0</v>
@@ -4943,16 +4943,16 @@
         <v>2300</v>
       </c>
       <c r="Q33" s="29" t="n">
-        <v>9927</v>
+        <v>11830</v>
       </c>
       <c r="R33" s="30" t="n">
-        <v>152109</v>
+        <v>162030</v>
       </c>
       <c r="S33" s="29" t="n">
-        <v>40315</v>
+        <v>60207</v>
       </c>
       <c r="T33" s="29" t="n">
-        <v>525831</v>
+        <v>674304</v>
       </c>
     </row>
     <row r="34">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="C34" s="29" t="n">
-        <v>140740</v>
+        <v>173826</v>
       </c>
       <c r="D34" s="29" t="n">
         <v>45144</v>
@@ -4977,7 +4977,7 @@
         <v>10996</v>
       </c>
       <c r="G34" s="30" t="n">
-        <v>212844</v>
+        <v>245930</v>
       </c>
       <c r="H34" s="11" t="n">
         <v>4</v>
@@ -4989,16 +4989,16 @@
         <v>85500</v>
       </c>
       <c r="K34" s="29" t="n">
-        <v>2095</v>
+        <v>2210</v>
       </c>
       <c r="L34" s="29" t="n">
         <v>4160</v>
       </c>
       <c r="M34" s="29" t="n">
-        <v>46826</v>
+        <v>54105</v>
       </c>
       <c r="N34" s="29" t="n">
-        <v>5197</v>
+        <v>6403</v>
       </c>
       <c r="O34" s="29" t="n">
         <v>0</v>
@@ -5007,16 +5007,16 @@
         <v>2300</v>
       </c>
       <c r="Q34" s="29" t="n">
-        <v>11011</v>
+        <v>13126</v>
       </c>
       <c r="R34" s="30" t="n">
-        <v>158376</v>
+        <v>169391</v>
       </c>
       <c r="S34" s="29" t="n">
-        <v>54467</v>
+        <v>76539</v>
       </c>
       <c r="T34" s="29" t="n">
-        <v>580298</v>
+        <v>750843</v>
       </c>
     </row>
     <row r="35">
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="C35" s="29" t="n">
-        <v>156421</v>
+        <v>193145</v>
       </c>
       <c r="D35" s="29" t="n">
         <v>48897</v>
@@ -5041,7 +5041,7 @@
         <v>12494</v>
       </c>
       <c r="G35" s="30" t="n">
-        <v>235219</v>
+        <v>271943</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>4</v>
@@ -5053,16 +5053,16 @@
         <v>85500</v>
       </c>
       <c r="K35" s="29" t="n">
-        <v>2149</v>
+        <v>2277</v>
       </c>
       <c r="L35" s="29" t="n">
         <v>4160</v>
       </c>
       <c r="M35" s="29" t="n">
-        <v>51748</v>
+        <v>59827</v>
       </c>
       <c r="N35" s="29" t="n">
-        <v>5769</v>
+        <v>7108</v>
       </c>
       <c r="O35" s="29" t="n">
         <v>0</v>
@@ -5071,16 +5071,16 @@
         <v>2300</v>
       </c>
       <c r="Q35" s="29" t="n">
-        <v>12207</v>
+        <v>14559</v>
       </c>
       <c r="R35" s="30" t="n">
-        <v>165262</v>
+        <v>177492</v>
       </c>
       <c r="S35" s="29" t="n">
-        <v>69957</v>
+        <v>94451</v>
       </c>
       <c r="T35" s="29" t="n">
-        <v>650255</v>
+        <v>845294</v>
       </c>
     </row>
     <row r="36">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="C36" s="29" t="n">
-        <v>173826</v>
+        <v>214589</v>
       </c>
       <c r="D36" s="29" t="n">
         <v>52918</v>
@@ -5105,7 +5105,7 @@
         <v>14070</v>
       </c>
       <c r="G36" s="30" t="n">
-        <v>259757</v>
+        <v>300520</v>
       </c>
       <c r="H36" s="11" t="n">
         <v>4</v>
@@ -5117,16 +5117,16 @@
         <v>88625</v>
       </c>
       <c r="K36" s="29" t="n">
-        <v>2210</v>
+        <v>2351</v>
       </c>
       <c r="L36" s="29" t="n">
         <v>4290</v>
       </c>
       <c r="M36" s="29" t="n">
-        <v>57147</v>
+        <v>66114</v>
       </c>
       <c r="N36" s="29" t="n">
-        <v>6403</v>
+        <v>7890</v>
       </c>
       <c r="O36" s="29" t="n">
         <v>2200</v>
@@ -5135,16 +5135,16 @@
         <v>2300</v>
       </c>
       <c r="Q36" s="29" t="n">
-        <v>13527</v>
+        <v>16143</v>
       </c>
       <c r="R36" s="30" t="n">
-        <v>178289</v>
+        <v>191868</v>
       </c>
       <c r="S36" s="29" t="n">
-        <v>81469</v>
+        <v>108651</v>
       </c>
       <c r="T36" s="29" t="n">
-        <v>731724</v>
+        <v>953945</v>
       </c>
     </row>
     <row r="37">
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="C37" s="29" t="n">
-        <v>193145</v>
+        <v>238393</v>
       </c>
       <c r="D37" s="29" t="n">
         <v>57226</v>
@@ -5169,7 +5169,7 @@
         <v>15733</v>
       </c>
       <c r="G37" s="30" t="n">
-        <v>286684</v>
+        <v>331932</v>
       </c>
       <c r="H37" s="11" t="n">
         <v>4</v>
@@ -5181,16 +5181,16 @@
         <v>88625</v>
       </c>
       <c r="K37" s="29" t="n">
-        <v>2277</v>
+        <v>2434</v>
       </c>
       <c r="L37" s="29" t="n">
         <v>4290</v>
       </c>
       <c r="M37" s="29" t="n">
-        <v>63070</v>
+        <v>73025</v>
       </c>
       <c r="N37" s="29" t="n">
-        <v>7108</v>
+        <v>8758</v>
       </c>
       <c r="O37" s="29" t="n">
         <v>0</v>
@@ -5199,16 +5199,16 @@
         <v>2300</v>
       </c>
       <c r="Q37" s="29" t="n">
-        <v>14987</v>
+        <v>17895</v>
       </c>
       <c r="R37" s="30" t="n">
-        <v>184418</v>
+        <v>199496</v>
       </c>
       <c r="S37" s="29" t="n">
-        <v>102266</v>
+        <v>132435</v>
       </c>
       <c r="T37" s="29" t="n">
-        <v>833990</v>
+        <v>1086381</v>
       </c>
     </row>
     <row r="38">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="C38" s="32" t="n">
-        <v>214589</v>
+        <v>264819</v>
       </c>
       <c r="D38" s="32" t="n">
         <v>61843</v>
@@ -5233,7 +5233,7 @@
         <v>17490</v>
       </c>
       <c r="G38" s="33" t="n">
-        <v>316249</v>
+        <v>366479</v>
       </c>
       <c r="H38" s="34" t="n">
         <v>4</v>
@@ -5245,16 +5245,16 @@
         <v>88625</v>
       </c>
       <c r="K38" s="32" t="n">
-        <v>2351</v>
+        <v>2526</v>
       </c>
       <c r="L38" s="32" t="n">
         <v>4290</v>
       </c>
       <c r="M38" s="32" t="n">
-        <v>69575</v>
+        <v>80625</v>
       </c>
       <c r="N38" s="32" t="n">
-        <v>7890</v>
+        <v>9721</v>
       </c>
       <c r="O38" s="32" t="n">
         <v>0</v>
@@ -5263,16 +5263,16 @@
         <v>2300</v>
       </c>
       <c r="Q38" s="32" t="n">
-        <v>16599</v>
+        <v>19834</v>
       </c>
       <c r="R38" s="33" t="n">
-        <v>193585</v>
+        <v>210329</v>
       </c>
       <c r="S38" s="32" t="n">
-        <v>122664</v>
+        <v>156150</v>
       </c>
       <c r="T38" s="32" t="n">
-        <v>956654</v>
+        <v>1242531</v>
       </c>
     </row>
     <row r="39">
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="C39" s="29" t="n">
-        <v>238393</v>
+        <v>294156</v>
       </c>
       <c r="D39" s="29" t="n">
         <v>66794</v>
@@ -5297,7 +5297,7 @@
         <v>19350</v>
       </c>
       <c r="G39" s="30" t="n">
-        <v>348730</v>
+        <v>404493</v>
       </c>
       <c r="H39" s="11" t="n">
         <v>4</v>
@@ -5309,16 +5309,16 @@
         <v>88625</v>
       </c>
       <c r="K39" s="29" t="n">
-        <v>2434</v>
+        <v>2628</v>
       </c>
       <c r="L39" s="29" t="n">
         <v>4290</v>
       </c>
       <c r="M39" s="29" t="n">
-        <v>76721</v>
+        <v>88989</v>
       </c>
       <c r="N39" s="29" t="n">
-        <v>8758</v>
+        <v>10790</v>
       </c>
       <c r="O39" s="29" t="n">
         <v>0</v>
@@ -5327,16 +5327,16 @@
         <v>2300</v>
       </c>
       <c r="Q39" s="29" t="n">
-        <v>18382</v>
+        <v>21980</v>
       </c>
       <c r="R39" s="30" t="n">
-        <v>203679</v>
+        <v>222274</v>
       </c>
       <c r="S39" s="29" t="n">
-        <v>145051</v>
+        <v>182219</v>
       </c>
       <c r="T39" s="29" t="n">
-        <v>1101705</v>
+        <v>1424750</v>
       </c>
     </row>
     <row r="40">
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="C40" s="29" t="n">
-        <v>264819</v>
+        <v>326726</v>
       </c>
       <c r="D40" s="29" t="n">
         <v>72103</v>
@@ -5361,7 +5361,7 @@
         <v>21322</v>
       </c>
       <c r="G40" s="30" t="n">
-        <v>384432</v>
+        <v>446340</v>
       </c>
       <c r="H40" s="11" t="n">
         <v>4</v>
@@ -5373,16 +5373,16 @@
         <v>88625</v>
       </c>
       <c r="K40" s="29" t="n">
-        <v>2526</v>
+        <v>2741</v>
       </c>
       <c r="L40" s="29" t="n">
         <v>4290</v>
       </c>
       <c r="M40" s="29" t="n">
-        <v>84575</v>
+        <v>98195</v>
       </c>
       <c r="N40" s="29" t="n">
-        <v>9721</v>
+        <v>11977</v>
       </c>
       <c r="O40" s="29" t="n">
         <v>0</v>
@@ -5391,16 +5391,16 @@
         <v>2300</v>
       </c>
       <c r="Q40" s="29" t="n">
-        <v>20355</v>
+        <v>24356</v>
       </c>
       <c r="R40" s="30" t="n">
-        <v>214800</v>
+        <v>235450</v>
       </c>
       <c r="S40" s="29" t="n">
-        <v>169632</v>
+        <v>210889</v>
       </c>
       <c r="T40" s="29" t="n">
-        <v>1271338</v>
+        <v>1635639</v>
       </c>
     </row>
     <row r="41">
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="C41" s="29" t="n">
-        <v>294156</v>
+        <v>362888</v>
       </c>
       <c r="D41" s="29" t="n">
         <v>77799</v>
@@ -5425,7 +5425,7 @@
         <v>23416</v>
       </c>
       <c r="G41" s="30" t="n">
-        <v>423692</v>
+        <v>492424</v>
       </c>
       <c r="H41" s="11" t="n">
         <v>4</v>
@@ -5437,16 +5437,16 @@
         <v>88625</v>
       </c>
       <c r="K41" s="29" t="n">
-        <v>2628</v>
+        <v>2866</v>
       </c>
       <c r="L41" s="29" t="n">
         <v>4290</v>
       </c>
       <c r="M41" s="29" t="n">
-        <v>93212</v>
+        <v>108333</v>
       </c>
       <c r="N41" s="29" t="n">
-        <v>10790</v>
+        <v>13295</v>
       </c>
       <c r="O41" s="29" t="n">
         <v>0</v>
@@ -5455,16 +5455,16 @@
         <v>2300</v>
       </c>
       <c r="Q41" s="29" t="n">
-        <v>22537</v>
+        <v>26987</v>
       </c>
       <c r="R41" s="30" t="n">
-        <v>227055</v>
+        <v>249989</v>
       </c>
       <c r="S41" s="29" t="n">
-        <v>196637</v>
+        <v>242435</v>
       </c>
       <c r="T41" s="29" t="n">
-        <v>1467975</v>
+        <v>1878074</v>
       </c>
     </row>
     <row r="42">
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="C42" s="29" t="n">
-        <v>326726</v>
+        <v>403037</v>
       </c>
       <c r="D42" s="29" t="n">
         <v>83910</v>
@@ -5489,7 +5489,7 @@
         <v>25643</v>
       </c>
       <c r="G42" s="30" t="n">
-        <v>466883</v>
+        <v>543194</v>
       </c>
       <c r="H42" s="11" t="n">
         <v>4</v>
@@ -5501,16 +5501,16 @@
         <v>90250</v>
       </c>
       <c r="K42" s="29" t="n">
-        <v>2741</v>
+        <v>3005</v>
       </c>
       <c r="L42" s="29" t="n">
         <v>4420</v>
       </c>
       <c r="M42" s="29" t="n">
-        <v>102714</v>
+        <v>119503</v>
       </c>
       <c r="N42" s="29" t="n">
-        <v>11977</v>
+        <v>14757</v>
       </c>
       <c r="O42" s="29" t="n">
         <v>1300</v>
@@ -5519,16 +5519,16 @@
         <v>2300</v>
       </c>
       <c r="Q42" s="29" t="n">
-        <v>24951</v>
+        <v>29901</v>
       </c>
       <c r="R42" s="30" t="n">
-        <v>243621</v>
+        <v>269092</v>
       </c>
       <c r="S42" s="29" t="n">
-        <v>223263</v>
+        <v>274102</v>
       </c>
       <c r="T42" s="29" t="n">
-        <v>1691238</v>
+        <v>2152176</v>
       </c>
     </row>
     <row r="43">
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="C43" s="29" t="n">
-        <v>362888</v>
+        <v>447615</v>
       </c>
       <c r="D43" s="29" t="n">
         <v>90469</v>
@@ -5553,7 +5553,7 @@
         <v>28012</v>
       </c>
       <c r="G43" s="30" t="n">
-        <v>514418</v>
+        <v>599145</v>
       </c>
       <c r="H43" s="11" t="n">
         <v>4</v>
@@ -5565,16 +5565,16 @@
         <v>90250</v>
       </c>
       <c r="K43" s="29" t="n">
-        <v>2866</v>
+        <v>3160</v>
       </c>
       <c r="L43" s="29" t="n">
         <v>4420</v>
       </c>
       <c r="M43" s="29" t="n">
-        <v>113172</v>
+        <v>131812</v>
       </c>
       <c r="N43" s="29" t="n">
-        <v>13295</v>
+        <v>16380</v>
       </c>
       <c r="O43" s="29" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>2300</v>
       </c>
       <c r="Q43" s="29" t="n">
-        <v>27624</v>
+        <v>33130</v>
       </c>
       <c r="R43" s="30" t="n">
-        <v>257221</v>
+        <v>285510</v>
       </c>
       <c r="S43" s="29" t="n">
-        <v>257197</v>
+        <v>313635</v>
       </c>
       <c r="T43" s="29" t="n">
-        <v>1948435</v>
+        <v>2465811</v>
       </c>
     </row>
     <row r="44">
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="C44" s="29" t="n">
-        <v>403037</v>
+        <v>497111</v>
       </c>
       <c r="D44" s="29" t="n">
         <v>97509</v>
@@ -5617,7 +5617,7 @@
         <v>30537</v>
       </c>
       <c r="G44" s="30" t="n">
-        <v>566751</v>
+        <v>660826</v>
       </c>
       <c r="H44" s="11" t="n">
         <v>4</v>
@@ -5629,16 +5629,16 @@
         <v>93250</v>
       </c>
       <c r="K44" s="29" t="n">
-        <v>3005</v>
+        <v>3332</v>
       </c>
       <c r="L44" s="29" t="n">
         <v>4550</v>
       </c>
       <c r="M44" s="29" t="n">
-        <v>124685</v>
+        <v>145382</v>
       </c>
       <c r="N44" s="29" t="n">
-        <v>14757</v>
+        <v>18182</v>
       </c>
       <c r="O44" s="29" t="n">
         <v>2200</v>
@@ -5647,16 +5647,16 @@
         <v>2300</v>
       </c>
       <c r="Q44" s="29" t="n">
-        <v>30584</v>
+        <v>36708</v>
       </c>
       <c r="R44" s="30" t="n">
-        <v>278988</v>
+        <v>310408</v>
       </c>
       <c r="S44" s="29" t="n">
-        <v>287764</v>
+        <v>350418</v>
       </c>
       <c r="T44" s="29" t="n">
-        <v>2236199</v>
+        <v>2816228</v>
       </c>
     </row>
     <row r="45">
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="C45" s="29" t="n">
-        <v>447615</v>
+        <v>552070</v>
       </c>
       <c r="D45" s="29" t="n">
         <v>105067</v>
@@ -5681,7 +5681,7 @@
         <v>33231</v>
       </c>
       <c r="G45" s="30" t="n">
-        <v>624388</v>
+        <v>728843</v>
       </c>
       <c r="H45" s="11" t="n">
         <v>4</v>
@@ -5693,16 +5693,16 @@
         <v>93250</v>
       </c>
       <c r="K45" s="29" t="n">
-        <v>3160</v>
+        <v>3522</v>
       </c>
       <c r="L45" s="29" t="n">
         <v>4550</v>
       </c>
       <c r="M45" s="29" t="n">
-        <v>137365</v>
+        <v>160345</v>
       </c>
       <c r="N45" s="29" t="n">
-        <v>16380</v>
+        <v>20182</v>
       </c>
       <c r="O45" s="29" t="n">
         <v>0</v>
@@ -5711,16 +5711,16 @@
         <v>2300</v>
       </c>
       <c r="Q45" s="29" t="n">
-        <v>33862</v>
+        <v>40675</v>
       </c>
       <c r="R45" s="30" t="n">
-        <v>294926</v>
+        <v>329825</v>
       </c>
       <c r="S45" s="29" t="n">
-        <v>329462</v>
+        <v>399018</v>
       </c>
       <c r="T45" s="29" t="n">
-        <v>2565661</v>
+        <v>3215247</v>
       </c>
     </row>
     <row r="46">
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="C46" s="29" t="n">
-        <v>497111</v>
+        <v>613095</v>
       </c>
       <c r="D46" s="29" t="n">
         <v>113182</v>
@@ -5745,7 +5745,7 @@
         <v>36106</v>
       </c>
       <c r="G46" s="30" t="n">
-        <v>687884</v>
+        <v>803868</v>
       </c>
       <c r="H46" s="11" t="n">
         <v>4</v>
@@ -5757,16 +5757,16 @@
         <v>93250</v>
       </c>
       <c r="K46" s="29" t="n">
-        <v>3332</v>
+        <v>3734</v>
       </c>
       <c r="L46" s="29" t="n">
         <v>4550</v>
       </c>
       <c r="M46" s="29" t="n">
-        <v>151334</v>
+        <v>176851</v>
       </c>
       <c r="N46" s="29" t="n">
-        <v>18182</v>
+        <v>22402</v>
       </c>
       <c r="O46" s="29" t="n">
         <v>0</v>
@@ -5775,16 +5775,16 @@
         <v>2300</v>
       </c>
       <c r="Q46" s="29" t="n">
-        <v>37493</v>
+        <v>45072</v>
       </c>
       <c r="R46" s="30" t="n">
-        <v>314946</v>
+        <v>353709</v>
       </c>
       <c r="S46" s="29" t="n">
-        <v>372938</v>
+        <v>450159</v>
       </c>
       <c r="T46" s="29" t="n">
-        <v>2938599</v>
+        <v>3665406</v>
       </c>
     </row>
     <row r="47">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="C47" s="29" t="n">
-        <v>552070</v>
+        <v>680857</v>
       </c>
       <c r="D47" s="29" t="n">
         <v>121896</v>
@@ -5809,7 +5809,7 @@
         <v>39178</v>
       </c>
       <c r="G47" s="30" t="n">
-        <v>757857</v>
+        <v>886643</v>
       </c>
       <c r="H47" s="11" t="n">
         <v>4</v>
@@ -5821,16 +5821,16 @@
         <v>93250</v>
       </c>
       <c r="K47" s="29" t="n">
-        <v>3522</v>
+        <v>3968</v>
       </c>
       <c r="L47" s="29" t="n">
         <v>4550</v>
       </c>
       <c r="M47" s="29" t="n">
-        <v>166728</v>
+        <v>195062</v>
       </c>
       <c r="N47" s="29" t="n">
-        <v>20182</v>
+        <v>24866</v>
       </c>
       <c r="O47" s="29" t="n">
         <v>0</v>
@@ -5839,16 +5839,16 @@
         <v>2300</v>
       </c>
       <c r="Q47" s="29" t="n">
-        <v>41516</v>
+        <v>49948</v>
       </c>
       <c r="R47" s="30" t="n">
-        <v>337049</v>
+        <v>380105</v>
       </c>
       <c r="S47" s="29" t="n">
-        <v>420808</v>
+        <v>506539</v>
       </c>
       <c r="T47" s="29" t="n">
-        <v>3359407</v>
+        <v>4171944</v>
       </c>
     </row>
     <row r="48">
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="C48" s="29" t="n">
-        <v>613095</v>
+        <v>756101</v>
       </c>
       <c r="D48" s="29" t="n">
         <v>131254</v>
@@ -5873,7 +5873,7 @@
         <v>42461</v>
       </c>
       <c r="G48" s="30" t="n">
-        <v>834987</v>
+        <v>977993</v>
       </c>
       <c r="H48" s="11" t="n">
         <v>4</v>
@@ -5885,16 +5885,16 @@
         <v>93250</v>
       </c>
       <c r="K48" s="29" t="n">
-        <v>3734</v>
+        <v>4229</v>
       </c>
       <c r="L48" s="29" t="n">
         <v>4550</v>
       </c>
       <c r="M48" s="29" t="n">
-        <v>183697</v>
+        <v>215158</v>
       </c>
       <c r="N48" s="29" t="n">
-        <v>22402</v>
+        <v>27602</v>
       </c>
       <c r="O48" s="29" t="n">
         <v>0</v>
@@ -5903,16 +5903,16 @@
         <v>2300</v>
       </c>
       <c r="Q48" s="29" t="n">
-        <v>45975</v>
+        <v>55356</v>
       </c>
       <c r="R48" s="30" t="n">
-        <v>361458</v>
+        <v>409283</v>
       </c>
       <c r="S48" s="29" t="n">
-        <v>473530</v>
+        <v>568710</v>
       </c>
       <c r="T48" s="29" t="n">
-        <v>3832936</v>
+        <v>4740654</v>
       </c>
     </row>
     <row r="49">
@@ -5925,7 +5925,7 @@
         </is>
       </c>
       <c r="C49" s="29" t="n">
-        <v>680857</v>
+        <v>839654</v>
       </c>
       <c r="D49" s="29" t="n">
         <v>141306</v>
@@ -5937,7 +5937,7 @@
         <v>45974</v>
       </c>
       <c r="G49" s="30" t="n">
-        <v>920030</v>
+        <v>1078827</v>
       </c>
       <c r="H49" s="11" t="n">
         <v>4</v>
@@ -5949,16 +5949,16 @@
         <v>93250</v>
       </c>
       <c r="K49" s="29" t="n">
-        <v>3968</v>
+        <v>4518</v>
       </c>
       <c r="L49" s="29" t="n">
         <v>4550</v>
       </c>
       <c r="M49" s="29" t="n">
-        <v>202407</v>
+        <v>237342</v>
       </c>
       <c r="N49" s="29" t="n">
-        <v>24866</v>
+        <v>30638</v>
       </c>
       <c r="O49" s="29" t="n">
         <v>0</v>
@@ -5967,16 +5967,16 @@
         <v>2300</v>
       </c>
       <c r="Q49" s="29" t="n">
-        <v>50916</v>
+        <v>61354</v>
       </c>
       <c r="R49" s="30" t="n">
-        <v>388418</v>
+        <v>441542</v>
       </c>
       <c r="S49" s="29" t="n">
-        <v>531612</v>
+        <v>637285</v>
       </c>
       <c r="T49" s="29" t="n">
-        <v>4364548</v>
+        <v>5377940</v>
       </c>
     </row>
     <row r="50">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="C50" s="32" t="n">
-        <v>756101</v>
+        <v>932435</v>
       </c>
       <c r="D50" s="32" t="n">
         <v>152103</v>
@@ -6001,7 +6001,7 @@
         <v>49734</v>
       </c>
       <c r="G50" s="33" t="n">
-        <v>1013820</v>
+        <v>1190154</v>
       </c>
       <c r="H50" s="34" t="n">
         <v>4</v>
@@ -6013,16 +6013,16 @@
         <v>93250</v>
       </c>
       <c r="K50" s="32" t="n">
-        <v>4229</v>
+        <v>4839</v>
       </c>
       <c r="L50" s="32" t="n">
         <v>4550</v>
       </c>
       <c r="M50" s="32" t="n">
-        <v>223040</v>
+        <v>261834</v>
       </c>
       <c r="N50" s="32" t="n">
-        <v>27602</v>
+        <v>34008</v>
       </c>
       <c r="O50" s="32" t="n">
         <v>0</v>
@@ -6031,16 +6031,16 @@
         <v>2300</v>
       </c>
       <c r="Q50" s="32" t="n">
-        <v>56395</v>
+        <v>68007</v>
       </c>
       <c r="R50" s="33" t="n">
-        <v>418204</v>
+        <v>477214</v>
       </c>
       <c r="S50" s="32" t="n">
-        <v>595616</v>
+        <v>712941</v>
       </c>
       <c r="T50" s="32" t="n">
-        <v>4960165</v>
+        <v>6090880</v>
       </c>
     </row>
     <row r="51">
@@ -6138,19 +6138,19 @@
         </is>
       </c>
       <c r="B3" s="10" t="n">
-        <v>79599</v>
+        <v>115540</v>
       </c>
       <c r="C3" s="10" t="n">
-        <v>418014</v>
+        <v>523126</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>1537436</v>
+        <v>1899594</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>5436867</v>
+        <v>6705744</v>
       </c>
       <c r="F3" s="36" t="n">
-        <v>7471916</v>
+        <v>9244004</v>
       </c>
     </row>
     <row r="4">
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>89763</v>
+        <v>125704</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>610781</v>
+        <v>715893</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>2317075</v>
+        <v>2679233</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>7543873</v>
+        <v>8812750</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>10561492</v>
+        <v>12333580</v>
       </c>
     </row>
     <row r="8">
@@ -6248,19 +6248,19 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>849882</v>
+        <v>902797</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>1178648</v>
+        <v>1222528</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>1832434</v>
+        <v>1952974</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>3540363</v>
+        <v>3964401</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>7401327</v>
+        <v>8042700</v>
       </c>
     </row>
     <row r="9">
@@ -6270,19 +6270,19 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>-760119</v>
+        <v>-777093</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>-567867</v>
+        <v>-506635</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>484641</v>
+        <v>726259</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>4003510</v>
+        <v>4848350</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>3160165</v>
+        <v>4290880</v>
       </c>
     </row>
     <row r="10">
@@ -6292,16 +6292,16 @@
         </is>
       </c>
       <c r="B10" s="37" t="n">
-        <v>1039881</v>
+        <v>1022907</v>
       </c>
       <c r="C10" s="37" t="n">
-        <v>472013</v>
+        <v>516272</v>
       </c>
       <c r="D10" s="37" t="n">
-        <v>956654</v>
+        <v>1242531</v>
       </c>
       <c r="E10" s="37" t="n">
-        <v>4960165</v>
+        <v>6090880</v>
       </c>
       <c r="F10" s="23" t="n"/>
     </row>
